--- a/data/nzd0603/nzd0603.xlsx
+++ b/data/nzd0603/nzd0603.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R372"/>
+  <dimension ref="A1:R374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22744,6 +22744,126 @@
         <v>226.5</v>
       </c>
       <c r="R372" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>236.31</v>
+      </c>
+      <c r="C373" t="n">
+        <v>223.22</v>
+      </c>
+      <c r="D373" t="n">
+        <v>230.37</v>
+      </c>
+      <c r="E373" t="n">
+        <v>225.27</v>
+      </c>
+      <c r="F373" t="n">
+        <v>218.17</v>
+      </c>
+      <c r="G373" t="n">
+        <v>225.43</v>
+      </c>
+      <c r="H373" t="n">
+        <v>212</v>
+      </c>
+      <c r="I373" t="n">
+        <v>215.7</v>
+      </c>
+      <c r="J373" t="n">
+        <v>220.69</v>
+      </c>
+      <c r="K373" t="n">
+        <v>281.26</v>
+      </c>
+      <c r="L373" t="n">
+        <v>318.32</v>
+      </c>
+      <c r="M373" t="n">
+        <v>234.45</v>
+      </c>
+      <c r="N373" t="n">
+        <v>220.91</v>
+      </c>
+      <c r="O373" t="n">
+        <v>217.11</v>
+      </c>
+      <c r="P373" t="n">
+        <v>242.72</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>225.76</v>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>236.88</v>
+      </c>
+      <c r="C374" t="n">
+        <v>224.54</v>
+      </c>
+      <c r="D374" t="n">
+        <v>231.63</v>
+      </c>
+      <c r="E374" t="n">
+        <v>226.79</v>
+      </c>
+      <c r="F374" t="n">
+        <v>219.55</v>
+      </c>
+      <c r="G374" t="n">
+        <v>226.92</v>
+      </c>
+      <c r="H374" t="n">
+        <v>213.45</v>
+      </c>
+      <c r="I374" t="n">
+        <v>217.77</v>
+      </c>
+      <c r="J374" t="n">
+        <v>221.9</v>
+      </c>
+      <c r="K374" t="n">
+        <v>283.58</v>
+      </c>
+      <c r="L374" t="n">
+        <v>320.36</v>
+      </c>
+      <c r="M374" t="n">
+        <v>234.45</v>
+      </c>
+      <c r="N374" t="n">
+        <v>221.89</v>
+      </c>
+      <c r="O374" t="n">
+        <v>217.11</v>
+      </c>
+      <c r="P374" t="n">
+        <v>242.72</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>229.04</v>
+      </c>
+      <c r="R374" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22760,7 +22880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B382"/>
+  <dimension ref="A1:B384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26583,6 +26703,26 @@
       </c>
       <c r="B382" t="n">
         <v>-0.97</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -26745,28 +26885,28 @@
         <v>0.0619</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07987034682192654</v>
+        <v>0.08379982702544909</v>
       </c>
       <c r="J2" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K2" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01570909208961968</v>
+        <v>0.0173886976351999</v>
       </c>
       <c r="M2" t="n">
-        <v>3.429704601556507</v>
+        <v>3.433171521067116</v>
       </c>
       <c r="N2" t="n">
-        <v>22.3611954568896</v>
+        <v>22.32142459384624</v>
       </c>
       <c r="O2" t="n">
-        <v>4.728762571422846</v>
+        <v>4.724555491667575</v>
       </c>
       <c r="P2" t="n">
-        <v>230.5900260112063</v>
+        <v>230.5483475594615</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26817,28 +26957,28 @@
         <v>0.0871</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1600472929700865</v>
+        <v>0.159551409910892</v>
       </c>
       <c r="J3" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K3" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05430104929347623</v>
+        <v>0.05453131948331835</v>
       </c>
       <c r="M3" t="n">
-        <v>3.49420341134748</v>
+        <v>3.478304881691688</v>
       </c>
       <c r="N3" t="n">
-        <v>24.90931605275887</v>
+        <v>24.77825314731094</v>
       </c>
       <c r="O3" t="n">
-        <v>4.99092336674877</v>
+        <v>4.977775923774687</v>
       </c>
       <c r="P3" t="n">
-        <v>220.1289781755426</v>
+        <v>220.1342453036134</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26889,28 +27029,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1976663611180972</v>
+        <v>0.1956293832047105</v>
       </c>
       <c r="J4" t="n">
+        <v>373</v>
+      </c>
+      <c r="K4" t="n">
         <v>371</v>
       </c>
-      <c r="K4" t="n">
-        <v>369</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.06028885848127219</v>
+        <v>0.05969071358641709</v>
       </c>
       <c r="M4" t="n">
-        <v>3.978886722864091</v>
+        <v>3.969401464684989</v>
       </c>
       <c r="N4" t="n">
-        <v>34.21105578132853</v>
+        <v>34.05031803854116</v>
       </c>
       <c r="O4" t="n">
-        <v>5.849021779864435</v>
+        <v>5.835265035843801</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7778647456925</v>
+        <v>227.7994334169388</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26961,28 +27101,28 @@
         <v>0.1326</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4619748731095388</v>
+        <v>0.4634685389140255</v>
       </c>
       <c r="J5" t="n">
+        <v>373</v>
+      </c>
+      <c r="K5" t="n">
         <v>371</v>
       </c>
-      <c r="K5" t="n">
-        <v>369</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2212641783606535</v>
+        <v>0.22419253418464</v>
       </c>
       <c r="M5" t="n">
-        <v>4.50204046704602</v>
+        <v>4.484776985034147</v>
       </c>
       <c r="N5" t="n">
-        <v>42.19484348455831</v>
+        <v>41.98192738270807</v>
       </c>
       <c r="O5" t="n">
-        <v>6.495755805490098</v>
+        <v>6.479346215684733</v>
       </c>
       <c r="P5" t="n">
-        <v>212.3009918423641</v>
+        <v>212.2851559903099</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27033,28 +27173,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3233674759152104</v>
+        <v>0.3271347823137549</v>
       </c>
       <c r="J6" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K6" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.126341369389697</v>
+        <v>0.1299292775356359</v>
       </c>
       <c r="M6" t="n">
-        <v>4.484798284788698</v>
+        <v>4.477594613812208</v>
       </c>
       <c r="N6" t="n">
-        <v>40.45203315343155</v>
+        <v>40.310848655505</v>
       </c>
       <c r="O6" t="n">
-        <v>6.360191282770633</v>
+        <v>6.349082505016375</v>
       </c>
       <c r="P6" t="n">
-        <v>206.5613974665215</v>
+        <v>206.5214322215579</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27105,28 +27245,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4442161359952628</v>
+        <v>0.4473864022979311</v>
       </c>
       <c r="J7" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K7" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2782060048331182</v>
+        <v>0.2828759221107301</v>
       </c>
       <c r="M7" t="n">
-        <v>3.865292289278262</v>
+        <v>3.859566338573823</v>
       </c>
       <c r="N7" t="n">
-        <v>28.64091672968623</v>
+        <v>28.54202925208111</v>
       </c>
       <c r="O7" t="n">
-        <v>5.351720912910746</v>
+        <v>5.342474075939078</v>
       </c>
       <c r="P7" t="n">
-        <v>211.2592380120729</v>
+        <v>211.2256038640597</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27177,28 +27317,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1331420284962241</v>
+        <v>0.131800740892798</v>
       </c>
       <c r="J8" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K8" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03461680842303039</v>
+        <v>0.03428840864980043</v>
       </c>
       <c r="M8" t="n">
-        <v>3.638420079861772</v>
+        <v>3.627673678126824</v>
       </c>
       <c r="N8" t="n">
-        <v>27.7129768064861</v>
+        <v>27.57613499186017</v>
       </c>
       <c r="O8" t="n">
-        <v>5.264311617532353</v>
+        <v>5.251298410094418</v>
       </c>
       <c r="P8" t="n">
-        <v>210.5255876356434</v>
+        <v>210.5397928614973</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27249,28 +27389,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1763801800914934</v>
+        <v>0.17692109333959</v>
       </c>
       <c r="J9" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K9" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07871912337225273</v>
+        <v>0.07993154984792372</v>
       </c>
       <c r="M9" t="n">
-        <v>3.04865804084557</v>
+        <v>3.037675606887101</v>
       </c>
       <c r="N9" t="n">
-        <v>20.36867881904649</v>
+        <v>20.26665612637912</v>
       </c>
       <c r="O9" t="n">
-        <v>4.513167271334677</v>
+        <v>4.501850300307543</v>
       </c>
       <c r="P9" t="n">
-        <v>211.526570648961</v>
+        <v>211.5208169013686</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27321,28 +27461,28 @@
         <v>0.0697</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.04460694375659439</v>
+        <v>-0.05802179095379412</v>
       </c>
       <c r="J10" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K10" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0008338400353397057</v>
+        <v>0.001415378005601764</v>
       </c>
       <c r="M10" t="n">
-        <v>9.235191550580536</v>
+        <v>9.245691431249448</v>
       </c>
       <c r="N10" t="n">
-        <v>133.3863535461619</v>
+        <v>133.6028295073033</v>
       </c>
       <c r="O10" t="n">
-        <v>11.5493009981627</v>
+        <v>11.55866901971431</v>
       </c>
       <c r="P10" t="n">
-        <v>235.7530984967386</v>
+        <v>235.8953586271196</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27393,28 +27533,28 @@
         <v>0.0313</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2712596245757051</v>
+        <v>-0.2488884116195687</v>
       </c>
       <c r="J11" t="n">
+        <v>373</v>
+      </c>
+      <c r="K11" t="n">
         <v>371</v>
       </c>
-      <c r="K11" t="n">
-        <v>369</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.02028510892961499</v>
+        <v>0.01709436509705886</v>
       </c>
       <c r="M11" t="n">
-        <v>10.6544253003222</v>
+        <v>10.76029490188251</v>
       </c>
       <c r="N11" t="n">
-        <v>199.3691658153287</v>
+        <v>200.8993725785023</v>
       </c>
       <c r="O11" t="n">
-        <v>14.11981465230081</v>
+        <v>14.1738975789478</v>
       </c>
       <c r="P11" t="n">
-        <v>267.4795692016289</v>
+        <v>267.2423149051277</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27465,28 +27605,28 @@
         <v>0.0382</v>
       </c>
       <c r="I12" t="n">
-        <v>1.204177661445423</v>
+        <v>1.261221059731428</v>
       </c>
       <c r="J12" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K12" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L12" t="n">
-        <v>0.223320156434984</v>
+        <v>0.2312624976499255</v>
       </c>
       <c r="M12" t="n">
-        <v>12.13385018349089</v>
+        <v>12.46317452604567</v>
       </c>
       <c r="N12" t="n">
-        <v>282.8907468674263</v>
+        <v>298.2236741023124</v>
       </c>
       <c r="O12" t="n">
-        <v>16.81935631549038</v>
+        <v>17.26915383284058</v>
       </c>
       <c r="P12" t="n">
-        <v>230.9778746031597</v>
+        <v>230.3737047254865</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27537,28 +27677,28 @@
         <v>0.1141</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4316399881143139</v>
+        <v>0.4274044136352081</v>
       </c>
       <c r="J13" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K13" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08251125633245904</v>
+        <v>0.08178203228945324</v>
       </c>
       <c r="M13" t="n">
-        <v>6.196882360127686</v>
+        <v>6.186538450572127</v>
       </c>
       <c r="N13" t="n">
-        <v>115.2043699068205</v>
+        <v>114.6769175255683</v>
       </c>
       <c r="O13" t="n">
-        <v>10.73332986108321</v>
+        <v>10.70873090172539</v>
       </c>
       <c r="P13" t="n">
-        <v>227.179475487179</v>
+        <v>227.2246072638989</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27609,28 +27749,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05197165639645696</v>
+        <v>0.05565348287083755</v>
       </c>
       <c r="J14" t="n">
+        <v>373</v>
+      </c>
+      <c r="K14" t="n">
         <v>371</v>
       </c>
-      <c r="K14" t="n">
-        <v>369</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.004143084586622048</v>
+        <v>0.004790111003722619</v>
       </c>
       <c r="M14" t="n">
-        <v>4.168790266321782</v>
+        <v>4.166907540482514</v>
       </c>
       <c r="N14" t="n">
-        <v>36.17661981770221</v>
+        <v>36.05250575671059</v>
       </c>
       <c r="O14" t="n">
-        <v>6.01470030988263</v>
+        <v>6.004373885486363</v>
       </c>
       <c r="P14" t="n">
-        <v>216.4007949027748</v>
+        <v>216.3615760882963</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27681,28 +27821,28 @@
         <v>0.1828</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.03728803603249795</v>
+        <v>-0.0458971565473727</v>
       </c>
       <c r="J15" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K15" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001361510791241471</v>
+        <v>0.002069764165099408</v>
       </c>
       <c r="M15" t="n">
-        <v>5.242353526348946</v>
+        <v>5.253045353869382</v>
       </c>
       <c r="N15" t="n">
-        <v>57.16975919378786</v>
+        <v>57.24643651010248</v>
       </c>
       <c r="O15" t="n">
-        <v>7.56106865421733</v>
+        <v>7.566137489505625</v>
       </c>
       <c r="P15" t="n">
-        <v>226.6158060210159</v>
+        <v>226.7070601689018</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27753,28 +27893,28 @@
         <v>0.0747</v>
       </c>
       <c r="I16" t="n">
-        <v>0.969629544624345</v>
+        <v>0.9618539450551377</v>
       </c>
       <c r="J16" t="n">
+        <v>373</v>
+      </c>
+      <c r="K16" t="n">
         <v>371</v>
       </c>
-      <c r="K16" t="n">
-        <v>369</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1577687118458746</v>
+        <v>0.1569227582896152</v>
       </c>
       <c r="M16" t="n">
-        <v>11.94533108842872</v>
+        <v>11.90483123164318</v>
       </c>
       <c r="N16" t="n">
-        <v>279.6687213513966</v>
+        <v>278.4718801929715</v>
       </c>
       <c r="O16" t="n">
-        <v>16.72329875806196</v>
+        <v>16.68747674733875</v>
       </c>
       <c r="P16" t="n">
-        <v>224.6656908925286</v>
+        <v>224.7484998467364</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27825,28 +27965,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3639865019289594</v>
+        <v>0.3564979252481232</v>
       </c>
       <c r="J17" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K17" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1085569003953933</v>
+        <v>0.1051445842755337</v>
       </c>
       <c r="M17" t="n">
-        <v>5.565025621838904</v>
+        <v>5.558216790653725</v>
       </c>
       <c r="N17" t="n">
-        <v>60.86368448888131</v>
+        <v>60.8416440196749</v>
       </c>
       <c r="O17" t="n">
-        <v>7.801518088736404</v>
+        <v>7.800105385164671</v>
       </c>
       <c r="P17" t="n">
-        <v>225.1649419610919</v>
+        <v>225.2443344250921</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27884,7 +28024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R372"/>
+  <dimension ref="A1:R374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62043,6 +62183,190 @@
         </is>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>-36.947486455689905,175.15217888975067</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>-36.94808648127741,175.15269785646677</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>-36.94849381437808,175.1533405424664</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>-36.94891576347854,175.1540712183293</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>-36.9493528918526,175.15478980808663</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>-36.949651087173656,175.15556408599744</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-36.95004800024155,175.15632881887277</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>-36.95030320731362,175.15716980032641</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>-36.95042096092683,175.1579780254677</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>-36.949935359677234,175.15892815055</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>-36.94966089329672,175.15985694157456</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>-36.95047248457501,175.16067603479107</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>-36.95041052668172,175.16144656689764</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>-36.95024864651458,175.16232279901934</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>-36.94969422527501,175.1628458868236</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>-36.94940110615636,175.1636879015355</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>-36.94748288365872,175.1521834875654</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>-36.94807820915827,175.1527085040589</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>-36.94848419212558,175.15334804971891</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-36.948904160354566,175.1540802840264</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>-36.94934235823643,175.1547980404095</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>-36.9496387621001,175.15557071848747</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-36.95003600650762,175.15633527466926</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>-36.95028608516484,175.1571790163681</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>-36.950410094027575,175.15797912373296</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>-36.94991452391922,175.15893025542297</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>-36.94964257219129,175.15985879218445</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>-36.95047248457501,175.16067603479107</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>-36.950402025727854,175.16144359066706</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>-36.95024864651458,175.16232279901934</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>-36.94969422527501,175.1628458868236</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>-36.94937703066799,175.16366654488633</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0603/nzd0603.xlsx
+++ b/data/nzd0603/nzd0603.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R374"/>
+  <dimension ref="A1:R375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22843,7 +22843,7 @@
         <v>221.9</v>
       </c>
       <c r="K374" t="n">
-        <v>283.58</v>
+        <v>285.16</v>
       </c>
       <c r="L374" t="n">
         <v>320.36</v>
@@ -22855,10 +22855,10 @@
         <v>221.89</v>
       </c>
       <c r="O374" t="n">
-        <v>217.11</v>
+        <v>224.3</v>
       </c>
       <c r="P374" t="n">
-        <v>242.72</v>
+        <v>247.52</v>
       </c>
       <c r="Q374" t="n">
         <v>229.04</v>
@@ -22866,6 +22866,66 @@
       <c r="R374" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>237.04</v>
+      </c>
+      <c r="C375" t="n">
+        <v>224.93</v>
+      </c>
+      <c r="D375" t="n">
+        <v>232.65</v>
+      </c>
+      <c r="E375" t="n">
+        <v>227.11</v>
+      </c>
+      <c r="F375" t="n">
+        <v>220.41</v>
+      </c>
+      <c r="G375" t="n">
+        <v>227.38</v>
+      </c>
+      <c r="H375" t="n">
+        <v>214.85</v>
+      </c>
+      <c r="I375" t="n">
+        <v>217.69</v>
+      </c>
+      <c r="J375" t="n">
+        <v>223.37</v>
+      </c>
+      <c r="K375" t="n">
+        <v>285.97</v>
+      </c>
+      <c r="L375" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="M375" t="n">
+        <v>236.72</v>
+      </c>
+      <c r="N375" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="O375" t="n">
+        <v>227.07</v>
+      </c>
+      <c r="P375" t="n">
+        <v>250.22</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>233.08</v>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -22880,7 +22940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B384"/>
+  <dimension ref="A1:B385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26723,6 +26783,16 @@
       </c>
       <c r="B384" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -26885,28 +26955,28 @@
         <v>0.0619</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08379982702544909</v>
+        <v>0.08594780954801508</v>
       </c>
       <c r="J2" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0173886976351999</v>
+        <v>0.01833293714899809</v>
       </c>
       <c r="M2" t="n">
-        <v>3.433171521067116</v>
+        <v>3.435853967381308</v>
       </c>
       <c r="N2" t="n">
-        <v>22.32142459384624</v>
+        <v>22.30994153392362</v>
       </c>
       <c r="O2" t="n">
-        <v>4.724555491667575</v>
+        <v>4.723340082391234</v>
       </c>
       <c r="P2" t="n">
-        <v>230.5483475594615</v>
+        <v>230.5255087328302</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26957,28 +27027,28 @@
         <v>0.0871</v>
       </c>
       <c r="I3" t="n">
-        <v>0.159551409910892</v>
+        <v>0.15983286047726</v>
       </c>
       <c r="J3" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K3" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05453131948331835</v>
+        <v>0.05499059377135096</v>
       </c>
       <c r="M3" t="n">
-        <v>3.478304881691688</v>
+        <v>3.470719583750371</v>
       </c>
       <c r="N3" t="n">
-        <v>24.77825314731094</v>
+        <v>24.71229177803353</v>
       </c>
       <c r="O3" t="n">
-        <v>4.977775923774687</v>
+        <v>4.971145922021756</v>
       </c>
       <c r="P3" t="n">
-        <v>220.1342453036134</v>
+        <v>220.1312418391522</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27029,28 +27099,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1956293832047105</v>
+        <v>0.1954534113880106</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05969071358641709</v>
+        <v>0.0598909498954121</v>
       </c>
       <c r="M4" t="n">
-        <v>3.969401464684989</v>
+        <v>3.959755635441322</v>
       </c>
       <c r="N4" t="n">
-        <v>34.05031803854116</v>
+        <v>33.95911052871686</v>
       </c>
       <c r="O4" t="n">
-        <v>5.835265035843801</v>
+        <v>5.827444596795138</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7994334169388</v>
+        <v>227.8013024373891</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27101,28 +27171,28 @@
         <v>0.1326</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4634685389140255</v>
+        <v>0.4647352489708722</v>
       </c>
       <c r="J5" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L5" t="n">
-        <v>0.22419253418464</v>
+        <v>0.2260113594000341</v>
       </c>
       <c r="M5" t="n">
-        <v>4.484776985034147</v>
+        <v>4.478658005954248</v>
       </c>
       <c r="N5" t="n">
-        <v>41.98192738270807</v>
+        <v>41.88594436145126</v>
       </c>
       <c r="O5" t="n">
-        <v>6.479346215684733</v>
+        <v>6.471935132667142</v>
       </c>
       <c r="P5" t="n">
-        <v>212.2851559903099</v>
+        <v>212.2717020915821</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27173,28 +27243,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3271347823137549</v>
+        <v>0.3297547805027611</v>
       </c>
       <c r="J6" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K6" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1299292775356359</v>
+        <v>0.1321561254501957</v>
       </c>
       <c r="M6" t="n">
-        <v>4.477594613812208</v>
+        <v>4.47731170735999</v>
       </c>
       <c r="N6" t="n">
-        <v>40.310848655505</v>
+        <v>40.27477676912138</v>
       </c>
       <c r="O6" t="n">
-        <v>6.349082505016375</v>
+        <v>6.346241152770778</v>
       </c>
       <c r="P6" t="n">
-        <v>206.5214322215579</v>
+        <v>206.4935745999133</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27245,28 +27315,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4473864022979311</v>
+        <v>0.4495356536520286</v>
       </c>
       <c r="J7" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2828759221107301</v>
+        <v>0.2855767300681731</v>
       </c>
       <c r="M7" t="n">
-        <v>3.859566338573823</v>
+        <v>3.859403392989712</v>
       </c>
       <c r="N7" t="n">
-        <v>28.54202925208111</v>
+        <v>28.51397052037472</v>
       </c>
       <c r="O7" t="n">
-        <v>5.342474075939078</v>
+        <v>5.339847424821679</v>
       </c>
       <c r="P7" t="n">
-        <v>211.2256038640597</v>
+        <v>211.2027515463395</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27317,28 +27387,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.131800740892798</v>
+        <v>0.1322080155014584</v>
       </c>
       <c r="J8" t="n">
+        <v>374</v>
+      </c>
+      <c r="K8" t="n">
         <v>373</v>
       </c>
-      <c r="K8" t="n">
-        <v>372</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.03428840864980043</v>
+        <v>0.03467075921998974</v>
       </c>
       <c r="M8" t="n">
-        <v>3.627673678126824</v>
+        <v>3.619580829836719</v>
       </c>
       <c r="N8" t="n">
-        <v>27.57613499186017</v>
+        <v>27.5039427839191</v>
       </c>
       <c r="O8" t="n">
-        <v>5.251298410094418</v>
+        <v>5.244420157073526</v>
       </c>
       <c r="P8" t="n">
-        <v>210.5397928614973</v>
+        <v>210.5354647244127</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27389,28 +27459,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17692109333959</v>
+        <v>0.1776611446104053</v>
       </c>
       <c r="J9" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K9" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07993154984792372</v>
+        <v>0.08092629259291262</v>
       </c>
       <c r="M9" t="n">
-        <v>3.037675606887101</v>
+        <v>3.033224721682271</v>
       </c>
       <c r="N9" t="n">
-        <v>20.26665612637912</v>
+        <v>20.21818868395786</v>
       </c>
       <c r="O9" t="n">
-        <v>4.501850300307543</v>
+        <v>4.496464020089325</v>
       </c>
       <c r="P9" t="n">
-        <v>211.5208169013686</v>
+        <v>211.5129481675708</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27461,28 +27531,28 @@
         <v>0.0697</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05802179095379412</v>
+        <v>-0.06355853914900048</v>
       </c>
       <c r="J10" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K10" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001415378005601764</v>
+        <v>0.00170297696176358</v>
       </c>
       <c r="M10" t="n">
-        <v>9.245691431249448</v>
+        <v>9.245548525561766</v>
       </c>
       <c r="N10" t="n">
-        <v>133.6028295073033</v>
+        <v>133.565856377047</v>
       </c>
       <c r="O10" t="n">
-        <v>11.55866901971431</v>
+        <v>11.5570695410665</v>
       </c>
       <c r="P10" t="n">
-        <v>235.8953586271196</v>
+        <v>235.9542291397066</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27533,28 +27603,28 @@
         <v>0.0313</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2488884116195687</v>
+        <v>-0.2353228593397972</v>
       </c>
       <c r="J11" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K11" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01709436509705886</v>
+        <v>0.01524732752675995</v>
       </c>
       <c r="M11" t="n">
-        <v>10.76029490188251</v>
+        <v>10.83252703074212</v>
       </c>
       <c r="N11" t="n">
-        <v>200.8993725785023</v>
+        <v>202.2719261097373</v>
       </c>
       <c r="O11" t="n">
-        <v>14.1738975789478</v>
+        <v>14.22223351340208</v>
       </c>
       <c r="P11" t="n">
-        <v>267.2423149051277</v>
+        <v>267.0980956000238</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27605,28 +27675,28 @@
         <v>0.0382</v>
       </c>
       <c r="I12" t="n">
-        <v>1.261221059731428</v>
+        <v>1.288893394378453</v>
       </c>
       <c r="J12" t="n">
+        <v>374</v>
+      </c>
+      <c r="K12" t="n">
         <v>373</v>
       </c>
-      <c r="K12" t="n">
-        <v>372</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.2312624976499255</v>
+        <v>0.2352292339859453</v>
       </c>
       <c r="M12" t="n">
-        <v>12.46317452604567</v>
+        <v>12.62247186900487</v>
       </c>
       <c r="N12" t="n">
-        <v>298.2236741023124</v>
+        <v>305.4452571202818</v>
       </c>
       <c r="O12" t="n">
-        <v>17.26915383284058</v>
+        <v>17.47699222178352</v>
       </c>
       <c r="P12" t="n">
-        <v>230.3737047254865</v>
+        <v>230.0798673477237</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27677,28 +27747,28 @@
         <v>0.1141</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4274044136352081</v>
+        <v>0.4264645353969398</v>
       </c>
       <c r="J13" t="n">
+        <v>374</v>
+      </c>
+      <c r="K13" t="n">
         <v>373</v>
       </c>
-      <c r="K13" t="n">
-        <v>372</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.08178203228945324</v>
+        <v>0.08185051657383968</v>
       </c>
       <c r="M13" t="n">
-        <v>6.186538450572127</v>
+        <v>6.175014458103085</v>
       </c>
       <c r="N13" t="n">
-        <v>114.6769175255683</v>
+        <v>114.3786285552311</v>
       </c>
       <c r="O13" t="n">
-        <v>10.70873090172539</v>
+        <v>10.69479446063509</v>
       </c>
       <c r="P13" t="n">
-        <v>227.2246072638989</v>
+        <v>227.2346476378154</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27749,28 +27819,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05565348287083755</v>
+        <v>0.0583672810485768</v>
       </c>
       <c r="J14" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K14" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L14" t="n">
-        <v>0.004790111003722619</v>
+        <v>0.005283242274927269</v>
       </c>
       <c r="M14" t="n">
-        <v>4.166907540482514</v>
+        <v>4.171141748222136</v>
       </c>
       <c r="N14" t="n">
-        <v>36.05250575671059</v>
+        <v>36.03216997330919</v>
       </c>
       <c r="O14" t="n">
-        <v>6.004373885486363</v>
+        <v>6.002680232471923</v>
       </c>
       <c r="P14" t="n">
-        <v>216.3615760882963</v>
+        <v>216.3326004129503</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27821,28 +27891,28 @@
         <v>0.1828</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0458971565473727</v>
+        <v>-0.04148489699762031</v>
       </c>
       <c r="J15" t="n">
+        <v>374</v>
+      </c>
+      <c r="K15" t="n">
         <v>373</v>
       </c>
-      <c r="K15" t="n">
-        <v>372</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.002069764165099408</v>
+        <v>0.001706047297246882</v>
       </c>
       <c r="M15" t="n">
-        <v>5.253045353869382</v>
+        <v>5.227143024640594</v>
       </c>
       <c r="N15" t="n">
-        <v>57.24643651010248</v>
+        <v>56.91341939154636</v>
       </c>
       <c r="O15" t="n">
-        <v>7.566137489505625</v>
+        <v>7.544098315342024</v>
       </c>
       <c r="P15" t="n">
-        <v>226.7070601689018</v>
+        <v>226.660210547233</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27893,28 +27963,28 @@
         <v>0.0747</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9618539450551377</v>
+        <v>0.9642380139141554</v>
       </c>
       <c r="J16" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K16" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1569227582896152</v>
+        <v>0.1583596176497278</v>
       </c>
       <c r="M16" t="n">
-        <v>11.90483123164318</v>
+        <v>11.8655535330402</v>
       </c>
       <c r="N16" t="n">
-        <v>278.4718801929715</v>
+        <v>277.5896073821223</v>
       </c>
       <c r="O16" t="n">
-        <v>16.68747674733875</v>
+        <v>16.66102059845441</v>
       </c>
       <c r="P16" t="n">
-        <v>224.7484998467364</v>
+        <v>224.7230714472335</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27965,28 +28035,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3564979252481232</v>
+        <v>0.3556751967886706</v>
       </c>
       <c r="J17" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K17" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1051445842755337</v>
+        <v>0.105205474061101</v>
       </c>
       <c r="M17" t="n">
-        <v>5.558216790653725</v>
+        <v>5.545870422221963</v>
       </c>
       <c r="N17" t="n">
-        <v>60.8416440196749</v>
+        <v>60.68603710058036</v>
       </c>
       <c r="O17" t="n">
-        <v>7.800105385164671</v>
+        <v>7.790124331522595</v>
       </c>
       <c r="P17" t="n">
-        <v>225.2443344250921</v>
+        <v>225.253082239589</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28024,7 +28094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R374"/>
+  <dimension ref="A1:R375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62328,7 +62398,7 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>-36.94991452391922,175.15893025542297</t>
+          <t>-36.94990033404949,175.15893168891358</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -62348,12 +62418,12 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>-36.95024864651458,175.16232279901934</t>
+          <t>-36.95018627745006,175.1623009625676</t>
         </is>
       </c>
       <c r="P374" t="inlineStr">
         <is>
-          <t>-36.94969422527501,175.1628458868236</t>
+          <t>-36.94965897329802,175.16281466729205</t>
         </is>
       </c>
       <c r="Q374" t="inlineStr">
@@ -62364,6 +62434,98 @@
       <c r="R374" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>-36.947481880983275,175.15218477818</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>-36.9480757651229,175.15271164993794</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>-36.94847640268276,175.1533541270172</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-36.94890171759156,175.15408219259388</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>-36.949335793808686,175.15480317069654</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-36.94963495704374,175.15557276610141</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>-36.950024426350424,175.15634150785027</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>-36.950286746890406,175.15717866019267</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>-36.9503968920921,175.15798045798877</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>-36.94989305949602,175.15893242380417</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>-36.94965658244839,175.15985737701223</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>-36.95045209784944,175.16067809383998</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>-36.950390662207695,175.1614396122375</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>-36.95016224931101,175.16229254992527</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>-36.949639144056874,175.1627971063184</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>-36.94934737670681,175.16364023976402</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
